--- a/back_end/data/warehouse/유상.xlsx
+++ b/back_end/data/warehouse/유상.xlsx
@@ -23,7 +23,7 @@
     <t>조회기간 :</t>
   </si>
   <si>
-    <t>2026-05-01 ~ 2026-05-29</t>
+    <t>2026-06-01 ~ 2026-06-05</t>
   </si>
   <si>
     <t>수탁품명</t>
@@ -89,94 +89,61 @@
     <t>콘테이너 No.</t>
   </si>
   <si>
-    <t>돈가브리(580888-1)</t>
-  </si>
-  <si>
-    <t>약 12.1Kg</t>
-  </si>
-  <si>
-    <t>ONEYBCNF09300500</t>
-  </si>
-  <si>
-    <t>2025-09-08</t>
+    <t>돈갈매기 E.355(931122-9)</t>
+  </si>
+  <si>
+    <t>10kg</t>
+  </si>
+  <si>
+    <t>MAEU251355661</t>
+  </si>
+  <si>
+    <t>2025-05-27</t>
   </si>
   <si>
     <t>통관</t>
   </si>
   <si>
-    <t>2025-05-06</t>
-  </si>
-  <si>
-    <t>스페인</t>
-  </si>
-  <si>
-    <t>프리오사</t>
+    <t>2025-01-30</t>
+  </si>
+  <si>
+    <t>아일랜드</t>
+  </si>
+  <si>
+    <t>로즈데라</t>
   </si>
   <si>
     <t>C/T</t>
   </si>
   <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>2025-09-18</t>
-  </si>
-  <si>
-    <t>2027-05-05</t>
-  </si>
-  <si>
-    <t>FSCU580888-1</t>
+    <t>1147</t>
+  </si>
+  <si>
+    <t>2025-08-22</t>
+  </si>
+  <si>
+    <t>2027-01-29</t>
+  </si>
+  <si>
+    <t>SUDU931122-9</t>
   </si>
   <si>
     <t xml:space="preserve">소     계</t>
   </si>
   <si>
-    <t>돈갈매기 E.355(931122-9)</t>
-  </si>
-  <si>
-    <t>10kg</t>
-  </si>
-  <si>
-    <t>MAEU251355661</t>
-  </si>
-  <si>
-    <t>2025-05-27</t>
-  </si>
-  <si>
-    <t>2025-01-30</t>
-  </si>
-  <si>
-    <t>아일랜드</t>
-  </si>
-  <si>
-    <t>로즈데라</t>
-  </si>
-  <si>
-    <t>1147</t>
-  </si>
-  <si>
-    <t>2025-08-22</t>
-  </si>
-  <si>
-    <t>2027-01-29</t>
-  </si>
-  <si>
-    <t>SUDU931122-9</t>
-  </si>
-  <si>
-    <t>우깐양 E.294(303871-4)</t>
+    <t>우깐양 E.294(803505-7)</t>
   </si>
   <si>
     <t>20Kg</t>
   </si>
   <si>
-    <t>MEDUUL881130</t>
-  </si>
-  <si>
-    <t>2026-03-05</t>
-  </si>
-  <si>
-    <t>2026-01-26</t>
+    <t>ONEYBNEG00746600</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
   </si>
   <si>
     <t>호주</t>
@@ -185,30 +152,6 @@
     <t>TEYS</t>
   </si>
   <si>
-    <t>692</t>
-  </si>
-  <si>
-    <t>2026-03-17</t>
-  </si>
-  <si>
-    <t>2028-01-25</t>
-  </si>
-  <si>
-    <t>MSDU303871-4</t>
-  </si>
-  <si>
-    <t>우깐양 E.294(803505-7)</t>
-  </si>
-  <si>
-    <t>ONEYBNEG00746600</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
     <t>696</t>
   </si>
   <si>
@@ -278,36 +221,6 @@
     <t>SEGU953012-4</t>
   </si>
   <si>
-    <t>우목심GFYG E.80(203170-2)</t>
-  </si>
-  <si>
-    <t>약 16.6Kg</t>
-  </si>
-  <si>
-    <t>ONEYBNEF09181700</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>2025-11-03</t>
-  </si>
-  <si>
-    <t>놀란</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>2026-01-07</t>
-  </si>
-  <si>
-    <t>2027-11-02</t>
-  </si>
-  <si>
-    <t>SZLU203170-2</t>
-  </si>
-  <si>
     <t>우삼겹양지 E.86M(852050-0)</t>
   </si>
   <si>
@@ -371,7 +284,7 @@
     <t>1/1</t>
   </si>
   <si>
-    <t>2026-05-29 09:39:04</t>
+    <t>2026-06-05 09:35:13</t>
   </si>
 </sst>
 </file>
@@ -655,13 +568,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>971550</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1139,18 +1052,18 @@
         <v>27</v>
       </c>
       <c r="D9" s="9">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="9">
         <v>0</v>
       </c>
       <c r="G9" s="9">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J9" s="9"/>
       <c t="s" r="K9" s="8">
@@ -1173,7 +1086,7 @@
       </c>
       <c r="S9" s="8"/>
       <c r="T9" s="9">
-        <v>341</v>
+        <v>238</v>
       </c>
       <c t="s" r="U9" s="11">
         <v>33</v>
@@ -1186,18 +1099,18 @@
         <v>34</v>
       </c>
       <c r="D10" s="12">
-        <v>1812</v>
+        <v>30</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12">
         <v>0</v>
       </c>
       <c r="G10" s="12">
-        <v>1812</v>
+        <v>0</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J10" s="12"/>
       <c r="K10" s="8"/>
@@ -1221,158 +1134,158 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c t="s" r="A11" s="13">
+      <c t="s" r="A11" s="8">
+        <v>26</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c t="s" r="C11" s="8">
+        <v>27</v>
+      </c>
+      <c r="D11" s="9">
+        <v>147</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9">
+        <v>147</v>
+      </c>
+      <c r="J11" s="9"/>
+      <c t="s" r="K11" s="8">
+        <v>28</v>
+      </c>
+      <c r="L11" s="8"/>
+      <c t="s" r="M11" s="10">
+        <v>29</v>
+      </c>
+      <c r="N11" s="10"/>
+      <c t="s" r="O11" s="10">
+        <v>30</v>
+      </c>
+      <c t="s" r="P11" s="10">
+        <v>31</v>
+      </c>
+      <c r="Q11" s="10"/>
+      <c t="s" r="R11" s="8">
+        <v>32</v>
+      </c>
+      <c r="S11" s="8"/>
+      <c r="T11" s="9">
+        <v>238</v>
+      </c>
+      <c t="s" r="U11" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customHeight="1">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c t="s" r="C12" s="10">
+        <v>34</v>
+      </c>
+      <c r="D12" s="12">
+        <v>1470</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12">
+        <v>1470</v>
+      </c>
+      <c r="J12" s="12"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c t="s" r="M12" s="8">
+        <v>35</v>
+      </c>
+      <c r="N12" s="8"/>
+      <c t="s" r="O12" s="10">
+        <v>36</v>
+      </c>
+      <c t="s" r="P12" s="10">
+        <v>37</v>
+      </c>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="9"/>
+      <c t="s" r="U12" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c t="s" r="A13" s="13">
         <v>39</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="14">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="14">
         <v>150</v>
       </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14">
-        <v>0</v>
-      </c>
-      <c r="G11" s="14">
+      <c r="E13" s="14"/>
+      <c r="F13" s="14">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14">
         <v>150</v>
       </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14">
-        <v>0</v>
-      </c>
-      <c r="J11" s="14"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="17"/>
-    </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="18">
-        <v>1812</v>
-      </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18">
-        <v>0</v>
-      </c>
-      <c r="G12" s="18">
-        <v>1812</v>
-      </c>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18">
-        <v>0</v>
-      </c>
-      <c r="J12" s="18"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="17"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c t="s" r="A13" s="8">
-        <v>40</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c t="s" r="C13" s="8">
-        <v>41</v>
-      </c>
-      <c r="D13" s="9">
-        <v>3</v>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9">
-        <v>0</v>
-      </c>
-      <c r="G13" s="9">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9">
-        <v>3</v>
-      </c>
-      <c r="J13" s="9"/>
-      <c t="s" r="K13" s="8">
-        <v>42</v>
-      </c>
-      <c r="L13" s="8"/>
-      <c t="s" r="M13" s="10">
-        <v>43</v>
-      </c>
-      <c r="N13" s="10"/>
-      <c t="s" r="O13" s="10">
-        <v>30</v>
-      </c>
-      <c t="s" r="P13" s="10">
-        <v>44</v>
-      </c>
-      <c r="Q13" s="10"/>
-      <c t="s" r="R13" s="8">
-        <v>45</v>
-      </c>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9">
-        <v>245</v>
-      </c>
-      <c t="s" r="U13" s="11">
-        <v>46</v>
-      </c>
+      <c r="J13" s="14"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="17"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c t="s" r="C14" s="10">
-        <v>34</v>
-      </c>
-      <c r="D14" s="12">
-        <v>30</v>
-      </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12">
-        <v>0</v>
-      </c>
-      <c r="G14" s="12">
-        <v>0</v>
-      </c>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12">
-        <v>30</v>
-      </c>
-      <c r="J14" s="12"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c t="s" r="M14" s="8">
-        <v>47</v>
-      </c>
-      <c r="N14" s="8"/>
-      <c t="s" r="O14" s="10">
-        <v>48</v>
-      </c>
-      <c t="s" r="P14" s="10">
-        <v>49</v>
-      </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="9"/>
-      <c t="s" r="U14" s="11">
-        <v>50</v>
-      </c>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="18">
+        <v>1500</v>
+      </c>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18">
+        <v>0</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18">
+        <v>1500</v>
+      </c>
+      <c r="J14" s="18"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="17"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c t="s" r="A15" s="8">
@@ -1383,7 +1296,7 @@
         <v>41</v>
       </c>
       <c r="D15" s="9">
-        <v>197</v>
+        <v>475</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="9">
@@ -1394,7 +1307,7 @@
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9">
-        <v>147</v>
+        <v>425</v>
       </c>
       <c r="J15" s="9"/>
       <c t="s" r="K15" s="8">
@@ -1417,7 +1330,7 @@
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="9">
-        <v>245</v>
+        <v>602</v>
       </c>
       <c t="s" r="U15" s="11">
         <v>46</v>
@@ -1430,18 +1343,18 @@
         <v>34</v>
       </c>
       <c r="D16" s="12">
-        <v>1970</v>
+        <v>9500</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="12">
         <v>0</v>
       </c>
       <c r="G16" s="12">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="12">
-        <v>1470</v>
+        <v>8500</v>
       </c>
       <c r="J16" s="12"/>
       <c r="K16" s="8"/>
@@ -1471,7 +1384,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="14">
-        <v>200</v>
+        <v>475</v>
       </c>
       <c r="E17" s="14"/>
       <c r="F17" s="14">
@@ -1482,7 +1395,7 @@
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="14">
-        <v>150</v>
+        <v>425</v>
       </c>
       <c r="J17" s="14"/>
       <c r="K17" s="15"/>
@@ -1502,18 +1415,18 @@
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="18">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="E18" s="18"/>
       <c r="F18" s="18">
         <v>0</v>
       </c>
       <c r="G18" s="18">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H18" s="18"/>
       <c r="I18" s="18">
-        <v>1500</v>
+        <v>8500</v>
       </c>
       <c r="J18" s="18"/>
       <c r="K18" s="15"/>
@@ -1537,14 +1450,14 @@
         <v>52</v>
       </c>
       <c r="D19" s="9">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="9">
         <v>0</v>
       </c>
       <c r="G19" s="9">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9">
@@ -1563,18 +1476,18 @@
         <v>30</v>
       </c>
       <c t="s" r="P19" s="10">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="Q19" s="10"/>
       <c t="s" r="R19" s="8">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="S19" s="8"/>
       <c r="T19" s="9">
-        <v>606</v>
+        <v>228</v>
       </c>
       <c t="s" r="U19" s="11">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1">
@@ -1584,38 +1497,38 @@
         <v>34</v>
       </c>
       <c r="D20" s="12">
-        <v>500</v>
+        <v>1.9199999999999999</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="12">
         <v>0</v>
       </c>
       <c r="G20" s="12">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="12">
-        <v>0</v>
+        <v>1.9199999999999999</v>
       </c>
       <c r="J20" s="12"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
       <c t="s" r="M20" s="8">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N20" s="8"/>
       <c t="s" r="O20" s="10">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c t="s" r="P20" s="10">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q20" s="10"/>
       <c r="R20" s="8"/>
       <c r="S20" s="8"/>
       <c r="T20" s="9"/>
       <c t="s" r="U20" s="11">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1625,14 +1538,14 @@
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
       <c r="D21" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="14">
         <v>0</v>
       </c>
       <c r="G21" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14">
@@ -1656,18 +1569,18 @@
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
       <c r="D22" s="18">
-        <v>500</v>
+        <v>1.9199999999999999</v>
       </c>
       <c r="E22" s="18"/>
       <c r="F22" s="18">
         <v>0</v>
       </c>
       <c r="G22" s="18">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H22" s="18"/>
       <c r="I22" s="18">
-        <v>0</v>
+        <v>1.9199999999999999</v>
       </c>
       <c r="J22" s="18"/>
       <c r="K22" s="15"/>
@@ -1684,51 +1597,51 @@
     </row>
     <row r="23" ht="18" customHeight="1">
       <c t="s" r="A23" s="8">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B23" s="8"/>
       <c t="s" r="C23" s="8">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D23" s="9">
-        <v>666</v>
+        <v>87</v>
       </c>
       <c r="E23" s="9"/>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="9">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9">
-        <v>475</v>
+        <v>87</v>
       </c>
       <c r="J23" s="9"/>
       <c t="s" r="K23" s="8">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L23" s="8"/>
       <c t="s" r="M23" s="10">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N23" s="10"/>
       <c t="s" r="O23" s="10">
         <v>30</v>
       </c>
       <c t="s" r="P23" s="10">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q23" s="10"/>
       <c t="s" r="R23" s="8">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="S23" s="8"/>
       <c r="T23" s="9">
-        <v>609</v>
+        <v>231</v>
       </c>
       <c t="s" r="U23" s="11">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1">
@@ -1738,18 +1651,18 @@
         <v>34</v>
       </c>
       <c r="D24" s="12">
-        <v>13320</v>
+        <v>2390.7600000000002</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12">
         <v>0</v>
       </c>
       <c r="G24" s="12">
-        <v>3820</v>
+        <v>0</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="12">
-        <v>9500</v>
+        <v>2390.7600000000002</v>
       </c>
       <c r="J24" s="12"/>
       <c r="K24" s="8"/>
@@ -1779,18 +1692,18 @@
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="14">
-        <v>666</v>
+        <v>87</v>
       </c>
       <c r="E25" s="14"/>
       <c r="F25" s="14">
         <v>0</v>
       </c>
       <c r="G25" s="14">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="14">
-        <v>475</v>
+        <v>87</v>
       </c>
       <c r="J25" s="14"/>
       <c r="K25" s="15"/>
@@ -1810,18 +1723,18 @@
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="18">
-        <v>13320</v>
+        <v>2390.7600000000002</v>
       </c>
       <c r="E26" s="18"/>
       <c r="F26" s="18">
         <v>0</v>
       </c>
       <c r="G26" s="18">
-        <v>3820</v>
+        <v>0</v>
       </c>
       <c r="H26" s="18"/>
       <c r="I26" s="18">
-        <v>9500</v>
+        <v>2390.7600000000002</v>
       </c>
       <c r="J26" s="18"/>
       <c r="K26" s="15"/>
@@ -1845,18 +1758,18 @@
         <v>71</v>
       </c>
       <c r="D27" s="9">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J27" s="9"/>
       <c t="s" r="K27" s="8">
@@ -1871,18 +1784,18 @@
         <v>30</v>
       </c>
       <c t="s" r="P27" s="10">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="Q27" s="10"/>
       <c t="s" r="R27" s="8">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="S27" s="8"/>
       <c r="T27" s="9">
-        <v>235</v>
+        <v>571</v>
       </c>
       <c t="s" r="U27" s="11">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1">
@@ -1892,1091 +1805,449 @@
         <v>34</v>
       </c>
       <c r="D28" s="12">
-        <v>932.32000000000005</v>
+        <v>90.349999999999994</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12">
         <v>0</v>
       </c>
       <c r="G28" s="12">
-        <v>930.39999999999998</v>
+        <v>0</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="12">
-        <v>1.9199999999999999</v>
+        <v>90.349999999999994</v>
       </c>
       <c r="J28" s="12"/>
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
       <c t="s" r="M28" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N28" s="8"/>
       <c t="s" r="O28" s="10">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c t="s" r="P28" s="10">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q28" s="10"/>
       <c r="R28" s="8"/>
       <c r="S28" s="8"/>
       <c r="T28" s="9"/>
       <c t="s" r="U28" s="11">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c t="s" r="A29" s="8">
+        <v>70</v>
+      </c>
+      <c r="B29" s="8"/>
+      <c t="s" r="C29" s="8">
+        <v>71</v>
+      </c>
+      <c r="D29" s="9">
+        <v>170</v>
+      </c>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9">
+        <v>0</v>
+      </c>
+      <c r="G29" s="9">
+        <v>35</v>
+      </c>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9">
+        <v>135</v>
+      </c>
+      <c r="J29" s="9"/>
+      <c t="s" r="K29" s="8">
+        <v>72</v>
+      </c>
+      <c r="L29" s="8"/>
+      <c t="s" r="M29" s="10">
+        <v>73</v>
+      </c>
+      <c r="N29" s="10"/>
+      <c t="s" r="O29" s="10">
+        <v>30</v>
+      </c>
+      <c t="s" r="P29" s="10">
+        <v>74</v>
+      </c>
+      <c r="Q29" s="10"/>
+      <c t="s" r="R29" s="8">
+        <v>64</v>
+      </c>
+      <c r="S29" s="8"/>
+      <c r="T29" s="9">
+        <v>571</v>
+      </c>
+      <c t="s" r="U29" s="11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" customHeight="1">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c t="s" r="C30" s="10">
+        <v>34</v>
+      </c>
+      <c r="D30" s="12">
+        <v>5125.5</v>
+      </c>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12">
+        <v>0</v>
+      </c>
+      <c r="G30" s="12">
+        <v>1055.3199999999999</v>
+      </c>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12">
+        <v>4070.1799999999998</v>
+      </c>
+      <c r="J30" s="12"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c t="s" r="M30" s="8">
+        <v>76</v>
+      </c>
+      <c r="N30" s="8"/>
+      <c t="s" r="O30" s="10">
         <v>77</v>
       </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c t="s" r="A29" s="13">
+      <c t="s" r="P30" s="10">
+        <v>78</v>
+      </c>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="8"/>
+      <c r="S30" s="8"/>
+      <c r="T30" s="9"/>
+      <c t="s" r="U30" s="11">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c t="s" r="A31" s="13">
         <v>39</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="14">
-        <v>40</v>
-      </c>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14">
-        <v>0</v>
-      </c>
-      <c r="G29" s="14">
-        <v>40</v>
-      </c>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14">
-        <v>0</v>
-      </c>
-      <c r="J29" s="14"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="17"/>
-    </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="18">
-        <v>932.32000000000005</v>
-      </c>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18">
-        <v>0</v>
-      </c>
-      <c r="G30" s="18">
-        <v>930.39999999999998</v>
-      </c>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18">
-        <v>1.9199999999999999</v>
-      </c>
-      <c r="J30" s="18"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="17"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c t="s" r="A31" s="8">
-        <v>78</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c t="s" r="C31" s="8">
-        <v>79</v>
-      </c>
-      <c r="D31" s="9">
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="14">
+        <v>173</v>
+      </c>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>35</v>
+      </c>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14">
+        <v>138</v>
+      </c>
+      <c r="J31" s="14"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="16"/>
+      <c r="S31" s="16"/>
+      <c r="T31" s="16"/>
+      <c r="U31" s="17"/>
+    </row>
+    <row r="32" ht="16.5" customHeight="1">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="18">
+        <v>5215.8500000000004</v>
+      </c>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18">
+        <v>0</v>
+      </c>
+      <c r="G32" s="18">
+        <v>1055.3199999999999</v>
+      </c>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18">
+        <v>4160.5299999999997</v>
+      </c>
+      <c r="J32" s="18"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="16"/>
+      <c r="S32" s="16"/>
+      <c r="T32" s="16"/>
+      <c r="U32" s="17"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c t="s" r="A33" s="8">
+        <v>80</v>
+      </c>
+      <c r="B33" s="8"/>
+      <c t="s" r="C33" s="8">
+        <v>81</v>
+      </c>
+      <c r="D33" s="9">
+        <v>12</v>
+      </c>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9">
+        <v>0</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0</v>
+      </c>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9">
+        <v>12</v>
+      </c>
+      <c r="J33" s="9"/>
+      <c t="s" r="K33" s="8">
+        <v>82</v>
+      </c>
+      <c r="L33" s="8"/>
+      <c t="s" r="M33" s="10">
+        <v>83</v>
+      </c>
+      <c r="N33" s="10"/>
+      <c t="s" r="O33" s="10">
+        <v>30</v>
+      </c>
+      <c t="s" r="P33" s="10">
+        <v>84</v>
+      </c>
+      <c r="Q33" s="10"/>
+      <c t="s" r="R33" s="8">
+        <v>64</v>
+      </c>
+      <c r="S33" s="8"/>
+      <c r="T33" s="9">
+        <v>564</v>
+      </c>
+      <c t="s" r="U33" s="11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" customHeight="1">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c t="s" r="C34" s="10">
+        <v>34</v>
+      </c>
+      <c r="D34" s="12">
+        <v>349.37</v>
+      </c>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12">
+        <v>0</v>
+      </c>
+      <c r="G34" s="12">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12">
+        <v>349.37</v>
+      </c>
+      <c r="J34" s="12"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c t="s" r="M34" s="8">
+        <v>85</v>
+      </c>
+      <c r="N34" s="8"/>
+      <c t="s" r="O34" s="10">
+        <v>48</v>
+      </c>
+      <c t="s" r="P34" s="10">
+        <v>86</v>
+      </c>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="8"/>
+      <c r="S34" s="8"/>
+      <c r="T34" s="9"/>
+      <c t="s" r="U34" s="11">
         <v>87</v>
       </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9">
-        <v>0</v>
-      </c>
-      <c r="G31" s="9">
-        <v>0</v>
-      </c>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9">
-        <v>87</v>
-      </c>
-      <c r="J31" s="9"/>
-      <c t="s" r="K31" s="8">
-        <v>80</v>
-      </c>
-      <c r="L31" s="8"/>
-      <c t="s" r="M31" s="10">
-        <v>81</v>
-      </c>
-      <c r="N31" s="10"/>
-      <c t="s" r="O31" s="10">
-        <v>30</v>
-      </c>
-      <c t="s" r="P31" s="10">
-        <v>82</v>
-      </c>
-      <c r="Q31" s="10"/>
-      <c t="s" r="R31" s="8">
-        <v>83</v>
-      </c>
-      <c r="S31" s="8"/>
-      <c r="T31" s="9">
-        <v>238</v>
-      </c>
-      <c t="s" r="U31" s="11">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" customHeight="1">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c t="s" r="C32" s="10">
-        <v>34</v>
-      </c>
-      <c r="D32" s="12">
-        <v>2390.7600000000002</v>
-      </c>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12">
-        <v>0</v>
-      </c>
-      <c r="G32" s="12">
-        <v>0</v>
-      </c>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12">
-        <v>2390.7600000000002</v>
-      </c>
-      <c r="J32" s="12"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c t="s" r="M32" s="8">
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c t="s" r="A35" s="13">
+        <v>39</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="14">
+        <v>12</v>
+      </c>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14">
+        <v>12</v>
+      </c>
+      <c r="J35" s="14"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="16"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="16"/>
+      <c r="Q35" s="16"/>
+      <c r="R35" s="16"/>
+      <c r="S35" s="16"/>
+      <c r="T35" s="16"/>
+      <c r="U35" s="17"/>
+    </row>
+    <row r="36" ht="16.5" customHeight="1">
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="18">
+        <v>349.37</v>
+      </c>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18">
+        <v>0</v>
+      </c>
+      <c r="G36" s="18">
+        <v>0</v>
+      </c>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18">
+        <v>349.37</v>
+      </c>
+      <c r="J36" s="18"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="16"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="16"/>
+      <c r="S36" s="16"/>
+      <c r="T36" s="16"/>
+      <c r="U36" s="17"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c t="s" r="A37" s="19">
+        <v>88</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="20">
+        <v>897</v>
+      </c>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20">
+        <v>0</v>
+      </c>
+      <c r="G37" s="20">
         <v>85</v>
       </c>
-      <c r="N32" s="8"/>
-      <c t="s" r="O32" s="10">
-        <v>86</v>
-      </c>
-      <c t="s" r="P32" s="10">
-        <v>87</v>
-      </c>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="8"/>
-      <c r="S32" s="8"/>
-      <c r="T32" s="9"/>
-      <c t="s" r="U32" s="11">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c t="s" r="A33" s="13">
-        <v>39</v>
-      </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="14">
-        <v>87</v>
-      </c>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14">
-        <v>0</v>
-      </c>
-      <c r="G33" s="14">
-        <v>0</v>
-      </c>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14">
-        <v>87</v>
-      </c>
-      <c r="J33" s="14"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="16"/>
-      <c r="S33" s="16"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="17"/>
-    </row>
-    <row r="34" ht="16.5" customHeight="1">
-      <c r="A34" s="13"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="18">
-        <v>2390.7600000000002</v>
-      </c>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18">
-        <v>0</v>
-      </c>
-      <c r="G34" s="18">
-        <v>0</v>
-      </c>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18">
-        <v>2390.7600000000002</v>
-      </c>
-      <c r="J34" s="18"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="16"/>
-      <c r="O34" s="16"/>
-      <c r="P34" s="16"/>
-      <c r="Q34" s="16"/>
-      <c r="R34" s="16"/>
-      <c r="S34" s="16"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="17"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c t="s" r="A35" s="8">
+      <c r="H37" s="20"/>
+      <c r="I37" s="20">
+        <v>812</v>
+      </c>
+      <c r="J37" s="20"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22"/>
+      <c r="R37" s="22"/>
+      <c r="S37" s="22"/>
+      <c r="T37" s="22"/>
+      <c r="U37" s="23"/>
+    </row>
+    <row r="38" ht="16.5" customHeight="1">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="24">
+        <v>18957.900000000001</v>
+      </c>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24">
+        <v>0</v>
+      </c>
+      <c r="G38" s="24">
+        <v>2055.3200000000002</v>
+      </c>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24">
+        <v>16902.580000000002</v>
+      </c>
+      <c r="J38" s="24"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22"/>
+      <c r="R38" s="22"/>
+      <c r="S38" s="22"/>
+      <c r="T38" s="22"/>
+      <c r="U38" s="23"/>
+    </row>
+    <row r="39" ht="1.5" customHeight="1"/>
+    <row r="40" ht="3.75" customHeight="1"/>
+    <row r="41" ht="1.5" customHeight="1">
+      <c t="s" r="A41" s="25">
         <v>89</v>
       </c>
-      <c r="B35" s="8"/>
-      <c t="s" r="C35" s="8">
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c t="s" r="J41" s="26">
         <v>90</v>
       </c>
-      <c r="D35" s="9">
-        <v>130</v>
-      </c>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9">
-        <v>0</v>
-      </c>
-      <c r="G35" s="9">
-        <v>130</v>
-      </c>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9">
-        <v>0</v>
-      </c>
-      <c r="J35" s="9"/>
-      <c t="s" r="K35" s="8">
+      <c r="K41" s="26"/>
+    </row>
+    <row r="42" ht="9.75" customHeight="1">
+      <c r="A42" s="25"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c t="s" r="S42" s="27">
         <v>91</v>
       </c>
-      <c r="L35" s="8"/>
-      <c t="s" r="M35" s="10">
-        <v>92</v>
-      </c>
-      <c r="N35" s="10"/>
-      <c t="s" r="O35" s="10">
-        <v>30</v>
-      </c>
-      <c t="s" r="P35" s="10">
-        <v>93</v>
-      </c>
-      <c r="Q35" s="10"/>
-      <c t="s" r="R35" s="8">
-        <v>56</v>
-      </c>
-      <c r="S35" s="8"/>
-      <c r="T35" s="9">
-        <v>522</v>
-      </c>
-      <c t="s" r="U35" s="11">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" customHeight="1">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c t="s" r="C36" s="10">
-        <v>34</v>
-      </c>
-      <c r="D36" s="12">
-        <v>2159.3000000000002</v>
-      </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12">
-        <v>0</v>
-      </c>
-      <c r="G36" s="12">
-        <v>2159.3000000000002</v>
-      </c>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12">
-        <v>0</v>
-      </c>
-      <c r="J36" s="12"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c t="s" r="M36" s="8">
-        <v>95</v>
-      </c>
-      <c r="N36" s="8"/>
-      <c t="s" r="O36" s="10">
-        <v>96</v>
-      </c>
-      <c t="s" r="P36" s="10">
-        <v>97</v>
-      </c>
-      <c r="Q36" s="10"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c t="s" r="U36" s="11">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c t="s" r="A37" s="8">
-        <v>89</v>
-      </c>
-      <c r="B37" s="8"/>
-      <c t="s" r="C37" s="8">
-        <v>90</v>
-      </c>
-      <c r="D37" s="9">
-        <v>17</v>
-      </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9">
-        <v>0</v>
-      </c>
-      <c r="G37" s="9">
-        <v>17</v>
-      </c>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9">
-        <v>0</v>
-      </c>
-      <c r="J37" s="9"/>
-      <c t="s" r="K37" s="8">
-        <v>91</v>
-      </c>
-      <c r="L37" s="8"/>
-      <c t="s" r="M37" s="10">
-        <v>92</v>
-      </c>
-      <c r="N37" s="10"/>
-      <c t="s" r="O37" s="10">
-        <v>30</v>
-      </c>
-      <c t="s" r="P37" s="10">
-        <v>93</v>
-      </c>
-      <c r="Q37" s="10"/>
-      <c t="s" r="R37" s="8">
-        <v>56</v>
-      </c>
-      <c r="S37" s="8"/>
-      <c r="T37" s="9">
-        <v>522</v>
-      </c>
-      <c t="s" r="U37" s="11">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c t="s" r="C38" s="10">
-        <v>34</v>
-      </c>
-      <c r="D38" s="12">
-        <v>283.01999999999998</v>
-      </c>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12">
-        <v>0</v>
-      </c>
-      <c r="G38" s="12">
-        <v>283.01999999999998</v>
-      </c>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12">
-        <v>0</v>
-      </c>
-      <c r="J38" s="12"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c t="s" r="M38" s="8">
-        <v>95</v>
-      </c>
-      <c r="N38" s="8"/>
-      <c t="s" r="O38" s="10">
-        <v>96</v>
-      </c>
-      <c t="s" r="P38" s="10">
-        <v>97</v>
-      </c>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="8"/>
-      <c r="S38" s="8"/>
-      <c r="T38" s="9"/>
-      <c t="s" r="U38" s="11">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c t="s" r="A39" s="13">
-        <v>39</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="14">
-        <v>147</v>
-      </c>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14">
-        <v>0</v>
-      </c>
-      <c r="G39" s="14">
-        <v>147</v>
-      </c>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14">
-        <v>0</v>
-      </c>
-      <c r="J39" s="14"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="16"/>
-      <c r="S39" s="16"/>
-      <c r="T39" s="16"/>
-      <c r="U39" s="17"/>
-    </row>
-    <row r="40" ht="16.5" customHeight="1">
-      <c r="A40" s="13"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="18">
-        <v>2442.3200000000002</v>
-      </c>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18">
-        <v>0</v>
-      </c>
-      <c r="G40" s="18">
-        <v>2442.3200000000002</v>
-      </c>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18">
-        <v>0</v>
-      </c>
-      <c r="J40" s="18"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="16"/>
-      <c r="S40" s="16"/>
-      <c r="T40" s="16"/>
-      <c r="U40" s="17"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c t="s" r="A41" s="8">
-        <v>99</v>
-      </c>
-      <c r="B41" s="8"/>
-      <c t="s" r="C41" s="8">
-        <v>100</v>
-      </c>
-      <c r="D41" s="9">
-        <v>0</v>
-      </c>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9">
-        <v>170</v>
-      </c>
-      <c r="G41" s="9">
-        <v>0</v>
-      </c>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9">
-        <v>170</v>
-      </c>
-      <c r="J41" s="9"/>
-      <c t="s" r="K41" s="8">
-        <v>101</v>
-      </c>
-      <c r="L41" s="8"/>
-      <c t="s" r="M41" s="10">
-        <v>102</v>
-      </c>
-      <c r="N41" s="10"/>
-      <c t="s" r="O41" s="10">
-        <v>30</v>
-      </c>
-      <c t="s" r="P41" s="10">
-        <v>103</v>
-      </c>
-      <c r="Q41" s="10"/>
-      <c t="s" r="R41" s="8">
-        <v>83</v>
-      </c>
-      <c r="S41" s="8"/>
-      <c r="T41" s="9">
-        <v>578</v>
-      </c>
-      <c t="s" r="U41" s="11">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" ht="16.5" customHeight="1">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c t="s" r="C42" s="10">
-        <v>34</v>
-      </c>
-      <c r="D42" s="12">
-        <v>0</v>
-      </c>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12">
-        <v>5125.5</v>
-      </c>
-      <c r="G42" s="12">
-        <v>0</v>
-      </c>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12">
-        <v>5125.5</v>
-      </c>
-      <c r="J42" s="12"/>
-      <c r="K42" s="8"/>
-      <c r="L42" s="8"/>
-      <c t="s" r="M42" s="8">
-        <v>105</v>
-      </c>
-      <c r="N42" s="8"/>
-      <c t="s" r="O42" s="10">
-        <v>106</v>
-      </c>
-      <c t="s" r="P42" s="10">
-        <v>107</v>
-      </c>
-      <c r="Q42" s="10"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c t="s" r="U42" s="11">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c t="s" r="A43" s="8">
-        <v>99</v>
-      </c>
-      <c r="B43" s="8"/>
-      <c t="s" r="C43" s="8">
-        <v>100</v>
-      </c>
-      <c r="D43" s="9">
-        <v>0</v>
-      </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9">
-        <v>88</v>
-      </c>
-      <c r="G43" s="9">
-        <v>88</v>
-      </c>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9">
-        <v>0</v>
-      </c>
-      <c r="J43" s="9"/>
-      <c t="s" r="K43" s="8">
-        <v>101</v>
-      </c>
-      <c r="L43" s="8"/>
-      <c t="s" r="M43" s="10">
-        <v>102</v>
-      </c>
-      <c r="N43" s="10"/>
-      <c t="s" r="O43" s="10">
-        <v>30</v>
-      </c>
-      <c t="s" r="P43" s="10">
-        <v>103</v>
-      </c>
-      <c r="Q43" s="10"/>
-      <c t="s" r="R43" s="8">
-        <v>83</v>
-      </c>
-      <c r="S43" s="8"/>
-      <c r="T43" s="9">
-        <v>578</v>
-      </c>
-      <c t="s" r="U43" s="11">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" ht="16.5" customHeight="1">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c t="s" r="C44" s="10">
-        <v>34</v>
-      </c>
-      <c r="D44" s="12">
-        <v>0</v>
-      </c>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12">
-        <v>2653.1999999999998</v>
-      </c>
-      <c r="G44" s="12">
-        <v>2653.1999999999998</v>
-      </c>
-      <c r="H44" s="12"/>
-      <c r="I44" s="12">
-        <v>0</v>
-      </c>
-      <c r="J44" s="12"/>
-      <c r="K44" s="8"/>
-      <c r="L44" s="8"/>
-      <c t="s" r="M44" s="8">
-        <v>105</v>
-      </c>
-      <c r="N44" s="8"/>
-      <c t="s" r="O44" s="10">
-        <v>106</v>
-      </c>
-      <c t="s" r="P44" s="10">
-        <v>107</v>
-      </c>
-      <c r="Q44" s="10"/>
-      <c r="R44" s="8"/>
-      <c r="S44" s="8"/>
-      <c r="T44" s="9"/>
-      <c t="s" r="U44" s="11">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c t="s" r="A45" s="8">
-        <v>99</v>
-      </c>
-      <c r="B45" s="8"/>
-      <c t="s" r="C45" s="8">
-        <v>100</v>
-      </c>
-      <c r="D45" s="9">
-        <v>0</v>
-      </c>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9">
-        <v>130</v>
-      </c>
-      <c r="G45" s="9">
-        <v>127</v>
-      </c>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9">
-        <v>3</v>
-      </c>
-      <c r="J45" s="9"/>
-      <c t="s" r="K45" s="8">
-        <v>101</v>
-      </c>
-      <c r="L45" s="8"/>
-      <c t="s" r="M45" s="10">
-        <v>102</v>
-      </c>
-      <c r="N45" s="10"/>
-      <c t="s" r="O45" s="10">
-        <v>30</v>
-      </c>
-      <c t="s" r="P45" s="10">
-        <v>103</v>
-      </c>
-      <c r="Q45" s="10"/>
-      <c t="s" r="R45" s="8">
-        <v>83</v>
-      </c>
-      <c r="S45" s="8"/>
-      <c r="T45" s="9">
-        <v>578</v>
-      </c>
-      <c t="s" r="U45" s="11">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="46" ht="16.5" customHeight="1">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c t="s" r="C46" s="10">
-        <v>34</v>
-      </c>
-      <c r="D46" s="12">
-        <v>0</v>
-      </c>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12">
-        <v>3919.5</v>
-      </c>
-      <c r="G46" s="12">
-        <v>3829.1500000000001</v>
-      </c>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12">
-        <v>90.349999999999994</v>
-      </c>
-      <c r="J46" s="12"/>
-      <c r="K46" s="8"/>
-      <c r="L46" s="8"/>
-      <c t="s" r="M46" s="8">
-        <v>105</v>
-      </c>
-      <c r="N46" s="8"/>
-      <c t="s" r="O46" s="10">
-        <v>106</v>
-      </c>
-      <c t="s" r="P46" s="10">
-        <v>107</v>
-      </c>
-      <c r="Q46" s="10"/>
-      <c r="R46" s="8"/>
-      <c r="S46" s="8"/>
-      <c r="T46" s="9"/>
-      <c t="s" r="U46" s="11">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c t="s" r="A47" s="13">
-        <v>39</v>
-      </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="14">
-        <v>0</v>
-      </c>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14">
-        <v>388</v>
-      </c>
-      <c r="G47" s="14">
-        <v>215</v>
-      </c>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14">
-        <v>173</v>
-      </c>
-      <c r="J47" s="14"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="16"/>
-      <c r="O47" s="16"/>
-      <c r="P47" s="16"/>
-      <c r="Q47" s="16"/>
-      <c r="R47" s="16"/>
-      <c r="S47" s="16"/>
-      <c r="T47" s="16"/>
-      <c r="U47" s="17"/>
-    </row>
-    <row r="48" ht="16.5" customHeight="1">
-      <c r="A48" s="13"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="18">
-        <v>0</v>
-      </c>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18">
-        <v>11698.200000000001</v>
-      </c>
-      <c r="G48" s="18">
-        <v>6482.3500000000004</v>
-      </c>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18">
-        <v>5215.8500000000004</v>
-      </c>
-      <c r="J48" s="18"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="16"/>
-      <c r="O48" s="16"/>
-      <c r="P48" s="16"/>
-      <c r="Q48" s="16"/>
-      <c r="R48" s="16"/>
-      <c r="S48" s="16"/>
-      <c r="T48" s="16"/>
-      <c r="U48" s="17"/>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c t="s" r="A49" s="8">
-        <v>109</v>
-      </c>
-      <c r="B49" s="8"/>
-      <c t="s" r="C49" s="8">
-        <v>110</v>
-      </c>
-      <c r="D49" s="9">
-        <v>0</v>
-      </c>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9">
-        <v>142</v>
-      </c>
-      <c r="G49" s="9">
-        <v>130</v>
-      </c>
-      <c r="H49" s="9"/>
-      <c r="I49" s="9">
-        <v>12</v>
-      </c>
-      <c r="J49" s="9"/>
-      <c t="s" r="K49" s="8">
-        <v>111</v>
-      </c>
-      <c r="L49" s="8"/>
-      <c t="s" r="M49" s="10">
-        <v>112</v>
-      </c>
-      <c r="N49" s="10"/>
-      <c t="s" r="O49" s="10">
-        <v>30</v>
-      </c>
-      <c t="s" r="P49" s="10">
-        <v>113</v>
-      </c>
-      <c r="Q49" s="10"/>
-      <c t="s" r="R49" s="8">
-        <v>83</v>
-      </c>
-      <c r="S49" s="8"/>
-      <c r="T49" s="9">
-        <v>571</v>
-      </c>
-      <c t="s" r="U49" s="11">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="50" ht="16.5" customHeight="1">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c t="s" r="C50" s="10">
-        <v>34</v>
-      </c>
-      <c r="D50" s="12">
-        <v>0</v>
-      </c>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12">
-        <v>4134.1899999999996</v>
-      </c>
-      <c r="G50" s="12">
-        <v>3784.8200000000002</v>
-      </c>
-      <c r="H50" s="12"/>
-      <c r="I50" s="12">
-        <v>349.37</v>
-      </c>
-      <c r="J50" s="12"/>
-      <c r="K50" s="8"/>
-      <c r="L50" s="8"/>
-      <c t="s" r="M50" s="8">
-        <v>114</v>
-      </c>
-      <c r="N50" s="8"/>
-      <c t="s" r="O50" s="10">
-        <v>67</v>
-      </c>
-      <c t="s" r="P50" s="10">
-        <v>115</v>
-      </c>
-      <c r="Q50" s="10"/>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
-      <c r="T50" s="9"/>
-      <c t="s" r="U50" s="11">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c t="s" r="A51" s="13">
-        <v>39</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="14">
-        <v>0</v>
-      </c>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14">
-        <v>142</v>
-      </c>
-      <c r="G51" s="14">
-        <v>130</v>
-      </c>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14">
-        <v>12</v>
-      </c>
-      <c r="J51" s="14"/>
-      <c r="K51" s="15"/>
-      <c r="L51" s="15"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="16"/>
-      <c r="O51" s="16"/>
-      <c r="P51" s="16"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="16"/>
-      <c r="S51" s="16"/>
-      <c r="T51" s="16"/>
-      <c r="U51" s="17"/>
-    </row>
-    <row r="52" ht="16.5" customHeight="1">
-      <c r="A52" s="13"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="18">
-        <v>0</v>
-      </c>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18">
-        <v>4134.1899999999996</v>
-      </c>
-      <c r="G52" s="18">
-        <v>3784.8200000000002</v>
-      </c>
-      <c r="H52" s="18"/>
-      <c r="I52" s="18">
-        <v>349.37</v>
-      </c>
-      <c r="J52" s="18"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="16"/>
-      <c r="O52" s="16"/>
-      <c r="P52" s="16"/>
-      <c r="Q52" s="16"/>
-      <c r="R52" s="16"/>
-      <c r="S52" s="16"/>
-      <c r="T52" s="16"/>
-      <c r="U52" s="17"/>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c t="s" r="A53" s="19">
-        <v>117</v>
-      </c>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="20">
-        <v>1315</v>
-      </c>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20">
-        <v>530</v>
-      </c>
-      <c r="G53" s="20">
-        <v>948</v>
-      </c>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20">
-        <v>897</v>
-      </c>
-      <c r="J53" s="20"/>
-      <c r="K53" s="21"/>
-      <c r="L53" s="21"/>
-      <c r="M53" s="22"/>
-      <c r="N53" s="22"/>
-      <c r="O53" s="22"/>
-      <c r="P53" s="22"/>
-      <c r="Q53" s="22"/>
-      <c r="R53" s="22"/>
-      <c r="S53" s="22"/>
-      <c r="T53" s="22"/>
-      <c r="U53" s="23"/>
-    </row>
-    <row r="54" ht="16.5" customHeight="1">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="24">
-        <v>23397.400000000001</v>
-      </c>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24">
-        <v>15832.389999999999</v>
-      </c>
-      <c r="G54" s="24">
-        <v>20271.889999999999</v>
-      </c>
-      <c r="H54" s="24"/>
-      <c r="I54" s="24">
-        <v>18957.900000000001</v>
-      </c>
-      <c r="J54" s="24"/>
-      <c r="K54" s="21"/>
-      <c r="L54" s="21"/>
-      <c r="M54" s="22"/>
-      <c r="N54" s="22"/>
-      <c r="O54" s="22"/>
-      <c r="P54" s="22"/>
-      <c r="Q54" s="22"/>
-      <c r="R54" s="22"/>
-      <c r="S54" s="22"/>
-      <c r="T54" s="22"/>
-      <c r="U54" s="23"/>
-    </row>
-    <row r="55" ht="1.5" customHeight="1"/>
-    <row r="56" ht="3.75" customHeight="1"/>
-    <row r="57" ht="1.5" customHeight="1">
-      <c t="s" r="A57" s="25">
-        <v>118</v>
-      </c>
-      <c r="B57" s="25"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25"/>
-      <c t="s" r="J57" s="26">
-        <v>119</v>
-      </c>
-      <c r="K57" s="26"/>
-    </row>
-    <row r="58" ht="9.75" customHeight="1">
-      <c r="A58" s="25"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="25"/>
-      <c r="D58" s="25"/>
-      <c r="J58" s="26"/>
-      <c r="K58" s="26"/>
-      <c t="s" r="S58" s="27">
-        <v>120</v>
-      </c>
-      <c r="T58" s="27"/>
-      <c r="U58" s="27"/>
-    </row>
-    <row r="59" ht="1.5" customHeight="1">
-      <c r="A59" s="25"/>
-      <c r="B59" s="25"/>
-      <c r="C59" s="25"/>
-      <c r="D59" s="25"/>
-      <c r="J59" s="26"/>
-      <c r="K59" s="26"/>
+      <c r="T42" s="27"/>
+      <c r="U42" s="27"/>
+    </row>
+    <row r="43" ht="1.5" customHeight="1">
+      <c r="A43" s="25"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="J43" s="26"/>
+      <c r="K43" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="358">
+  <mergeCells count="239">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="B3:U3"/>
     <mergeCell ref="B5:U5"/>
@@ -3010,35 +2281,35 @@
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="R10:S10"/>
-    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="A11:B12"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L12"/>
-    <mergeCell ref="M11:N12"/>
-    <mergeCell ref="O11:P12"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="R11:T12"/>
-    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="T11:T12"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="I12:J12"/>
-    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="A13:C14"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="K13:L14"/>
+    <mergeCell ref="M13:N14"/>
+    <mergeCell ref="O13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="R13:T14"/>
+    <mergeCell ref="U13:U14"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="R14:S14"/>
     <mergeCell ref="A15:B16"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="G15:H15"/>
@@ -3142,199 +2413,80 @@
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="P28:Q28"/>
     <mergeCell ref="R28:S28"/>
-    <mergeCell ref="A29:C30"/>
+    <mergeCell ref="A29:B30"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:L30"/>
-    <mergeCell ref="M29:N30"/>
-    <mergeCell ref="O29:P30"/>
-    <mergeCell ref="Q29:Q30"/>
-    <mergeCell ref="R29:T30"/>
-    <mergeCell ref="U29:U30"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="T29:T30"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="I30:J30"/>
-    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="A31:C32"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="I31:J31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="T31:T32"/>
+    <mergeCell ref="K31:L32"/>
+    <mergeCell ref="M31:N32"/>
+    <mergeCell ref="O31:P32"/>
+    <mergeCell ref="Q31:Q32"/>
+    <mergeCell ref="R31:T32"/>
+    <mergeCell ref="U31:U32"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="G32:H32"/>
     <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="A33:B34"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K33:L34"/>
-    <mergeCell ref="M33:N34"/>
-    <mergeCell ref="O33:P34"/>
-    <mergeCell ref="Q33:Q34"/>
-    <mergeCell ref="R33:T34"/>
-    <mergeCell ref="U33:U34"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="T33:T34"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="G34:H34"/>
     <mergeCell ref="I34:J34"/>
-    <mergeCell ref="A35:B36"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="A35:C36"/>
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="G35:H35"/>
     <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:T36"/>
+    <mergeCell ref="K35:L36"/>
+    <mergeCell ref="M35:N36"/>
+    <mergeCell ref="O35:P36"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="R35:T36"/>
+    <mergeCell ref="U35:U36"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="G36:H36"/>
     <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="A37:B38"/>
+    <mergeCell ref="A37:C38"/>
     <mergeCell ref="D37:E37"/>
     <mergeCell ref="G37:H37"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="T37:T38"/>
+    <mergeCell ref="K37:L38"/>
+    <mergeCell ref="M37:N38"/>
+    <mergeCell ref="O37:P38"/>
+    <mergeCell ref="Q37:Q38"/>
+    <mergeCell ref="R37:T38"/>
+    <mergeCell ref="U37:U38"/>
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="P38:Q38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="M39:N40"/>
-    <mergeCell ref="O39:P40"/>
-    <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="R39:T40"/>
-    <mergeCell ref="U39:U40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="A41:B42"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="T41:T42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="A43:B44"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="T43:T44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="A45:B46"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="P45:Q45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="T45:T46"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="P46:Q46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="K47:L48"/>
-    <mergeCell ref="M47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="Q47:Q48"/>
-    <mergeCell ref="R47:T48"/>
-    <mergeCell ref="U47:U48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="A49:B50"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="T49:T50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="M50:N50"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:L52"/>
-    <mergeCell ref="M51:N52"/>
-    <mergeCell ref="O51:P52"/>
-    <mergeCell ref="Q51:Q52"/>
-    <mergeCell ref="R51:T52"/>
-    <mergeCell ref="U51:U52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="A53:C54"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="K53:L54"/>
-    <mergeCell ref="M53:N54"/>
-    <mergeCell ref="O53:P54"/>
-    <mergeCell ref="Q53:Q54"/>
-    <mergeCell ref="R53:T54"/>
-    <mergeCell ref="U53:U54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="A57:D59"/>
-    <mergeCell ref="J57:K59"/>
-    <mergeCell ref="S58:U58"/>
+    <mergeCell ref="A41:D43"/>
+    <mergeCell ref="J41:K43"/>
+    <mergeCell ref="S42:U42"/>
   </mergeCells>
   <pageMargins left="0.3937007784843445" right="0.3937007784843445" top="0.19291338324546814" bottom="0.27559053897857666" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>
